--- a/Department_BillableData_APM.xlsx
+++ b/Department_BillableData_APM.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Billable Type</t>
   </si>
@@ -21,6 +21,9 @@
   </si>
   <si>
     <t>APM</t>
+  </si>
+  <si>
+    <t>Bench</t>
   </si>
   <si>
     <t>Fixed Cost</t>
@@ -117,7 +120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.328125" customWidth="true" bestFit="true"/>
@@ -142,7 +145,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="4">
@@ -150,7 +153,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>3.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="5">
@@ -158,7 +161,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="6">
@@ -166,7 +169,15 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>42.0</v>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>53.0</v>
       </c>
     </row>
   </sheetData>

--- a/Department_BillableData_APM.xlsx
+++ b/Department_BillableData_APM.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Billable Type</t>
   </si>
@@ -30,9 +30,6 @@
   </si>
   <si>
     <t>InternalRNDProducts</t>
-  </si>
-  <si>
-    <t>Shadow</t>
   </si>
   <si>
     <t>TNM</t>
@@ -120,7 +117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.328125" customWidth="true" bestFit="true"/>
@@ -145,7 +142,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="4">
@@ -169,14 +166,6 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="n">
         <v>53.0</v>
       </c>
     </row>
